--- a/data/trans_orig/P45C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>356380</t>
+          <t>354423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394510</t>
+          <t>392478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321423</t>
+          <t>319057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358069</t>
+          <t>357288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687556</t>
+          <t>685006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>741767</t>
+          <t>739270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86769</t>
+          <t>87163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121374</t>
+          <t>125382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100776</t>
+          <t>100851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137062</t>
+          <t>137167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196655</t>
+          <t>196249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250006</t>
+          <t>252012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32489</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556055</t>
+          <t>554446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>600574</t>
+          <t>598867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490386</t>
+          <t>488193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>528371</t>
+          <t>526613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1056808</t>
+          <t>1055512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1116552</t>
+          <t>1116532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118282</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162074</t>
+          <t>162698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86594</t>
+          <t>85838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>123971</t>
+          <t>123441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>217052</t>
+          <t>215746</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274644</t>
+          <t>274053</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>37706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>525064</t>
+          <t>525085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>559911</t>
+          <t>561382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>593326</t>
+          <t>592067</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>625910</t>
+          <t>625423</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1129301</t>
+          <t>1125796</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1178040</t>
+          <t>1176251</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72788</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106724</t>
+          <t>106186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76732</t>
+          <t>77655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126804</t>
+          <t>127437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173006</t>
+          <t>174431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28662</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>417834</t>
+          <t>416675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>452144</t>
+          <t>450800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>449044</t>
+          <t>449380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>475865</t>
+          <t>474969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>874217</t>
+          <t>875669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>920006</t>
+          <t>919300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53586</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>89399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>55475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93545</t>
+          <t>93958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136867</t>
+          <t>136282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>335445</t>
+          <t>336532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>359047</t>
+          <t>358596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>363611</t>
+          <t>364777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>384647</t>
+          <t>385964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>707909</t>
+          <t>708043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>737624</t>
+          <t>737889</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44734</t>
+          <t>43036</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>41245</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68710</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267616</t>
+          <t>266862</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282985</t>
+          <t>282562</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>318433</t>
+          <t>319549</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334333</t>
+          <t>334120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>592894</t>
+          <t>592247</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>613067</t>
+          <t>613464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189089</t>
+          <t>189770</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>203217</t>
+          <t>203469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>320106</t>
+          <t>320248</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>330490</t>
+          <t>330442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>513485</t>
+          <t>515277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>531716</t>
+          <t>532083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>418229</t>
+          <t>418862</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>500237</t>
+          <t>500495</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>327798</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>400883</t>
+          <t>398378</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>770046</t>
+          <t>765457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>875580</t>
+          <t>876218</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>72746</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42023</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>71951</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>91197</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>135990</t>
+          <t>133070</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>287533</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327624</t>
+          <t>325707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278817</t>
+          <t>277593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>315507</t>
+          <t>315373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>578295</t>
+          <t>579492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>630125</t>
+          <t>632787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117725</t>
+          <t>120469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157764</t>
+          <t>158146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102725</t>
+          <t>103455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138905</t>
+          <t>140042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232215</t>
+          <t>230689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284179</t>
+          <t>283647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488950</t>
+          <t>489079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>535980</t>
+          <t>533788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500763</t>
+          <t>500201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536047</t>
+          <t>536223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005342</t>
+          <t>1003040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1062709</t>
+          <t>1062821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128358</t>
+          <t>128782</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174175</t>
+          <t>172448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97789</t>
+          <t>98041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>203294</t>
+          <t>203786</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258092</t>
+          <t>258945</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39061</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>547492</t>
+          <t>544552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>586249</t>
+          <t>585984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576130</t>
+          <t>576051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>616473</t>
+          <t>615666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1136351</t>
+          <t>1132564</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1190087</t>
+          <t>1188840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88754</t>
+          <t>89859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127686</t>
+          <t>131552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75515</t>
+          <t>74347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113088</t>
+          <t>111870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174141</t>
+          <t>174720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227110</t>
+          <t>230069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30877</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>487478</t>
+          <t>488810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>523978</t>
+          <t>524972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>522875</t>
+          <t>522982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>556141</t>
+          <t>556381</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1023496</t>
+          <t>1021674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1072643</t>
+          <t>1071183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74894</t>
+          <t>74184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109927</t>
+          <t>110050</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43030</t>
+          <t>43377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>73228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126827</t>
+          <t>126906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173885</t>
+          <t>173750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23658</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,47 +6260,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>23379</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>14925</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>34083</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>23379</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>14696</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>34558</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>371566</t>
+          <t>370101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>395866</t>
+          <t>394930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>390394</t>
+          <t>390081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>415764</t>
+          <t>414968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>770966</t>
+          <t>769511</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>806547</t>
+          <t>804477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52328</t>
+          <t>53673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>26746</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49221</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59899</t>
+          <t>62017</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>94731</t>
+          <t>95186</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274739</t>
+          <t>274338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292962</t>
+          <t>292934</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>318907</t>
+          <t>317380</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>336353</t>
+          <t>336490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>599391</t>
+          <t>599855</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>624120</t>
+          <t>625217</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28390</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>26881</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229430</t>
+          <t>229744</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241364</t>
+          <t>241421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>349821</t>
+          <t>350457</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>368020</t>
+          <t>367423</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>586577</t>
+          <t>586017</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>606428</t>
+          <t>606171</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,47 +7515,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>22543</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>14286</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>33219</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>22543</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>14255</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>33134</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -7578,97 +7578,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>2185</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>7599</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>7516</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2185</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>7722</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2756401</t>
+          <t>2757294</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2845146</t>
+          <t>2847854</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3007026</t>
+          <t>3008035</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3092545</t>
+          <t>3091474</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5787084</t>
+          <t>5786272</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5907200</t>
+          <t>5910210</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>508777</t>
+          <t>508366</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>596814</t>
+          <t>598366</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>379623</t>
+          <t>378936</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>455893</t>
+          <t>459093</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>917121</t>
+          <t>913835</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1031628</t>
+          <t>1027388</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>59551</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42517</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>72634</t>
+          <t>72597</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>82646</t>
+          <t>82768</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>124239</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295160</t>
+          <t>296701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331378</t>
+          <t>331672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279202</t>
+          <t>281686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313302</t>
+          <t>314029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>585793</t>
+          <t>586146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>633618</t>
+          <t>635674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112828</t>
+          <t>111957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>68627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102140</t>
+          <t>100867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156369</t>
+          <t>156499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202624</t>
+          <t>205648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455212</t>
+          <t>456736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492745</t>
+          <t>494961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418573</t>
+          <t>416978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457104</t>
+          <t>455243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>882559</t>
+          <t>887944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>937158</t>
+          <t>941677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86486</t>
+          <t>85109</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122156</t>
+          <t>121993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99928</t>
+          <t>100216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138833</t>
+          <t>139953</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>198198</t>
+          <t>193597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>248408</t>
+          <t>246438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22596</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>567082</t>
+          <t>567187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>600824</t>
+          <t>600915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>549717</t>
+          <t>550707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>583694</t>
+          <t>584850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1129616</t>
+          <t>1124059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1177217</t>
+          <t>1174338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60096</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93300</t>
+          <t>92360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>68715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103811</t>
+          <t>103359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136228</t>
+          <t>138459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184109</t>
+          <t>187851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>546484</t>
+          <t>547575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>580858</t>
+          <t>579550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>554485</t>
+          <t>552203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>586286</t>
+          <t>586081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1111004</t>
+          <t>1110739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1159688</t>
+          <t>1157566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60003</t>
+          <t>61126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93748</t>
+          <t>93086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48445</t>
+          <t>48243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77946</t>
+          <t>80134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114397</t>
+          <t>117279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161522</t>
+          <t>162271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>409642</t>
+          <t>408996</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437882</t>
+          <t>436598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>425408</t>
+          <t>425780</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>454662</t>
+          <t>454826</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>845905</t>
+          <t>844568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>884398</t>
+          <t>883265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60628</t>
+          <t>61965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,47 +10451,47 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>47301</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>34820</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>62182</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>47301</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>34780</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>62336</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76070</t>
+          <t>76599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113019</t>
+          <t>115127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>297114</t>
+          <t>296699</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315931</t>
+          <t>315935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>332640</t>
+          <t>330917</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>354055</t>
+          <t>352825</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>637637</t>
+          <t>637871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>665241</t>
+          <t>665876</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38336</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>33192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>233175</t>
+          <t>232468</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>246305</t>
+          <t>245810</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>370555</t>
+          <t>371478</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>387854</t>
+          <t>387723</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>609979</t>
+          <t>608927</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>631087</t>
+          <t>630746</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>18240</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2864354</t>
+          <t>2868558</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2948237</t>
+          <t>2953974</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,49 +11706,49 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>3040762</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>3001178</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3082182</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>86,43%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>87,61%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>3040762</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>3001273</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3081033</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>5633</t>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5890471</t>
+          <t>5896891</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6012886</t>
+          <t>6007079</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>387485</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>468427</t>
+          <t>461787</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>399464</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>477621</t>
+          <t>478903</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>801589</t>
+          <t>807294</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>918331</t>
+          <t>912590</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44332</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54585</t>
+          <t>53496</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>54591</t>
+          <t>55294</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>284316</t>
+          <t>283822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>341704</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222928</t>
+          <t>224268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>262746</t>
+          <t>262267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524901</t>
+          <t>519311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591029</t>
+          <t>591595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53642</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112204</t>
+          <t>109268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>46920</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>84044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112110</t>
+          <t>112017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177795</t>
+          <t>181203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288389</t>
+          <t>289467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335598</t>
+          <t>335240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>397256</t>
+          <t>398607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455694</t>
+          <t>458588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699579</t>
+          <t>698368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>779752</t>
+          <t>783861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79298</t>
+          <t>79222</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124338</t>
+          <t>125550</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>46445</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99714</t>
+          <t>99011</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135232</t>
+          <t>133884</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>211543</t>
+          <t>212124</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>402271</t>
+          <t>400210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>439621</t>
+          <t>440560</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>442699</t>
+          <t>442671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>470649</t>
+          <t>469870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>854402</t>
+          <t>854277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>902329</t>
+          <t>900912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83129</t>
+          <t>81817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119233</t>
+          <t>119997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>61809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89253</t>
+          <t>87925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151141</t>
+          <t>152339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197834</t>
+          <t>196834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>31464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>742306</t>
+          <t>738508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>844787</t>
+          <t>841994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>600342</t>
+          <t>601575</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>632733</t>
+          <t>635024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1360081</t>
+          <t>1360030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1481470</t>
+          <t>1487387</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126924</t>
+          <t>129509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>65976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98814</t>
+          <t>96968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104145</t>
+          <t>97501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209510</t>
+          <t>208756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18968</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>469867</t>
+          <t>469931</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>499327</t>
+          <t>499910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>471123</t>
+          <t>472097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>494206</t>
+          <t>495073</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>948870</t>
+          <t>948758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>987234</t>
+          <t>986349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>49971</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76585</t>
+          <t>76496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67238</t>
+          <t>65716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>100438</t>
+          <t>101904</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>136156</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13143</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>30055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>323662</t>
+          <t>322826</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>341343</t>
+          <t>341309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>561622</t>
+          <t>561561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>596980</t>
+          <t>598088</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>893103</t>
+          <t>892375</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>945335</t>
+          <t>944476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40700</t>
+          <t>41572</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>41129</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>28502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75025</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>253108</t>
+          <t>254380</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267160</t>
+          <t>267597</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>399455</t>
+          <t>398787</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>411233</t>
+          <t>410934</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>657110</t>
+          <t>656986</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>675281</t>
+          <t>675351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>48389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>374</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2856241</t>
+          <t>2850514</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3024612</t>
+          <t>3036571</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3158006</t>
+          <t>3160073</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3287351</t>
+          <t>3291561</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6044835</t>
+          <t>6040436</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6255466</t>
+          <t>6261619</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>376730</t>
+          <t>368642</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>537618</t>
+          <t>540816</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>326841</t>
+          <t>319593</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>445398</t>
+          <t>442190</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>756719</t>
+          <t>760892</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>952492</t>
+          <t>956689</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>74710</t>
+          <t>77503</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>38216</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>85001</t>
+          <t>84783</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>134634</t>
+          <t>132144</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>354423</t>
+          <t>355889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392478</t>
+          <t>392543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>319057</t>
+          <t>321551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357288</t>
+          <t>358340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>685006</t>
+          <t>687559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>739270</t>
+          <t>739059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87163</t>
+          <t>86918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125382</t>
+          <t>121645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>100237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137167</t>
+          <t>135972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196249</t>
+          <t>199667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252012</t>
+          <t>247530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>554446</t>
+          <t>554809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>598867</t>
+          <t>599473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488193</t>
+          <t>487924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>526613</t>
+          <t>527519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1055512</t>
+          <t>1059909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1116532</t>
+          <t>1117452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121199</t>
+          <t>120995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85838</t>
+          <t>86804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>123441</t>
+          <t>125773</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215746</t>
+          <t>215201</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274053</t>
+          <t>271727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>525085</t>
+          <t>525532</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>561382</t>
+          <t>560687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592067</t>
+          <t>590689</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>625423</t>
+          <t>623823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1125796</t>
+          <t>1129125</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1176251</t>
+          <t>1179761</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>71925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106186</t>
+          <t>106400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>47658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77655</t>
+          <t>77738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127437</t>
+          <t>126524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174431</t>
+          <t>172348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34302</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>416675</t>
+          <t>415810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>450800</t>
+          <t>449668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>449380</t>
+          <t>447439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>474969</t>
+          <t>474885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>875669</t>
+          <t>875256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>919300</t>
+          <t>919510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56959</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89399</t>
+          <t>89268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,82 +2229,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>42175</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>30980</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>56157</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>113513</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>93064</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>135118</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>11,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>42175</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30748</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>55475</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>113513</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>93958</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>136282</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>336532</t>
+          <t>337185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>358596</t>
+          <t>359349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>364777</t>
+          <t>364057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>385964</t>
+          <t>384251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>708023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>737889</t>
+          <t>739370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43036</t>
+          <t>43436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>68319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266862</t>
+          <t>266392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282562</t>
+          <t>282493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>319549</t>
+          <t>319490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334120</t>
+          <t>334546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>592247</t>
+          <t>592281</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>613464</t>
+          <t>613208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189770</t>
+          <t>189392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>203469</t>
+          <t>203304</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,82 +3484,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>327078</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>321157</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>330500</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>525005</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>515668</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>531758</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>96,94%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>327078</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>320248</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>330442</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>525005</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>515277</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>532083</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>418862</t>
+          <t>417405</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>500495</t>
+          <t>501386</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>327905</t>
+          <t>328046</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>398378</t>
+          <t>398532</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>765457</t>
+          <t>771904</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>876218</t>
+          <t>871480</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>72746</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>73097</t>
+          <t>72232</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>136039</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>287579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>325707</t>
+          <t>325797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>277593</t>
+          <t>278318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>315373</t>
+          <t>315897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>579492</t>
+          <t>577666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>632787</t>
+          <t>634855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120469</t>
+          <t>118390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158146</t>
+          <t>157288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103455</t>
+          <t>102630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140042</t>
+          <t>140370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230689</t>
+          <t>226982</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283647</t>
+          <t>282759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489079</t>
+          <t>491022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>533788</t>
+          <t>537023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500201</t>
+          <t>498683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536223</t>
+          <t>535113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003040</t>
+          <t>997202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1062821</t>
+          <t>1058701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128782</t>
+          <t>128686</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>172268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64197</t>
+          <t>65090</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98041</t>
+          <t>99474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>203786</t>
+          <t>204119</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258945</t>
+          <t>261133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>544552</t>
+          <t>547060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>585984</t>
+          <t>587083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576051</t>
+          <t>574847</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>615666</t>
+          <t>614264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1132564</t>
+          <t>1133813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1188840</t>
+          <t>1191816</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89859</t>
+          <t>88081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131552</t>
+          <t>127664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74347</t>
+          <t>74752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111870</t>
+          <t>113419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174720</t>
+          <t>176117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230069</t>
+          <t>229782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>488810</t>
+          <t>486751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>524972</t>
+          <t>523620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>522982</t>
+          <t>522601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>556381</t>
+          <t>555700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1021674</t>
+          <t>1021401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1071183</t>
+          <t>1072129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74184</t>
+          <t>75996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110050</t>
+          <t>110556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43377</t>
+          <t>43192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73228</t>
+          <t>72696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126906</t>
+          <t>126401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173750</t>
+          <t>173427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34083</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>370101</t>
+          <t>370789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394930</t>
+          <t>395471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>390081</t>
+          <t>390572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>769511</t>
+          <t>770188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>804477</t>
+          <t>804199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29411</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53673</t>
+          <t>53135</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26746</t>
+          <t>26842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>61706</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95186</t>
+          <t>94334</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274338</t>
+          <t>272836</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292934</t>
+          <t>291536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>317380</t>
+          <t>318052</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>336490</t>
+          <t>337301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>599855</t>
+          <t>597436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>625217</t>
+          <t>624388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48335</t>
+          <t>49005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229744</t>
+          <t>229703</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241421</t>
+          <t>241395</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>350457</t>
+          <t>351095</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>367423</t>
+          <t>367268</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>586017</t>
+          <t>585712</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>606171</t>
+          <t>605574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>33666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2757294</t>
+          <t>2755487</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2847854</t>
+          <t>2847553</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3008035</t>
+          <t>3006014</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3091474</t>
+          <t>3085325</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5786272</t>
+          <t>5790644</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5910210</t>
+          <t>5910279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>508366</t>
+          <t>507133</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>598366</t>
+          <t>598562</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>378936</t>
+          <t>382536</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>459093</t>
+          <t>458186</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>913835</t>
+          <t>910374</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1027388</t>
+          <t>1031273</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>72597</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>82768</t>
+          <t>79250</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>124239</t>
+          <t>120888</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>296701</t>
+          <t>295779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331672</t>
+          <t>331207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281686</t>
+          <t>281892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314029</t>
+          <t>313718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>586146</t>
+          <t>587994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>635674</t>
+          <t>637696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77079</t>
+          <t>75871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111957</t>
+          <t>112682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68627</t>
+          <t>69316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100867</t>
+          <t>101017</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156499</t>
+          <t>155818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205648</t>
+          <t>204031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456736</t>
+          <t>454690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494961</t>
+          <t>492846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416978</t>
+          <t>417486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455243</t>
+          <t>455542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887944</t>
+          <t>884722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941677</t>
+          <t>938943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85109</t>
+          <t>86432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121993</t>
+          <t>124494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100216</t>
+          <t>100190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139953</t>
+          <t>137047</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>193597</t>
+          <t>197319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>246438</t>
+          <t>247826</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>567187</t>
+          <t>566078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>600915</t>
+          <t>600012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550707</t>
+          <t>552239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584850</t>
+          <t>586189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124059</t>
+          <t>1127262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1174338</t>
+          <t>1175068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59459</t>
+          <t>59303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92360</t>
+          <t>92040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68715</t>
+          <t>67112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103359</t>
+          <t>100930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138459</t>
+          <t>139688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187851</t>
+          <t>185355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>547575</t>
+          <t>546365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>579550</t>
+          <t>580964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>552203</t>
+          <t>552671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>586081</t>
+          <t>585388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1110739</t>
+          <t>1110616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1157566</t>
+          <t>1155580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61126</t>
+          <t>59970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93086</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>48541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80134</t>
+          <t>78961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117279</t>
+          <t>117490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162271</t>
+          <t>161609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>408996</t>
+          <t>408532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>436598</t>
+          <t>437123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>425780</t>
+          <t>424638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>454826</t>
+          <t>454335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>844568</t>
+          <t>844492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883265</t>
+          <t>884797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>34336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61965</t>
+          <t>61835</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62182</t>
+          <t>63517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76599</t>
+          <t>74898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115127</t>
+          <t>112069</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>296699</t>
+          <t>298369</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315935</t>
+          <t>316081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>330917</t>
+          <t>331535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>352825</t>
+          <t>352894</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>637871</t>
+          <t>637007</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>665876</t>
+          <t>664910</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>37905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60222</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>232468</t>
+          <t>231862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245810</t>
+          <t>245841</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>371478</t>
+          <t>372000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>387723</t>
+          <t>387622</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>608927</t>
+          <t>609801</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>630746</t>
+          <t>630912</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23266</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>34538</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2868558</t>
+          <t>2872186</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2953974</t>
+          <t>2953273</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3001178</t>
+          <t>2997251</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3082182</t>
+          <t>3080889</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5896891</t>
+          <t>5892567</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6007079</t>
+          <t>6007281</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>381603</t>
+          <t>382515</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>461787</t>
+          <t>461252</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>398811</t>
+          <t>400362</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>478903</t>
+          <t>478364</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>807294</t>
+          <t>807743</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>912590</t>
+          <t>914266</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>43526</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>53496</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55294</t>
+          <t>53130</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>91240</t>
+          <t>88717</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>316686</t>
+          <t>319886</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283822</t>
+          <t>294499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>244295</t>
+          <t>285936</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>224268</t>
+          <t>263403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>262267</t>
+          <t>305204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>560980</t>
+          <t>605822</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>519311</t>
+          <t>572256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591595</t>
+          <t>639241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76929</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52533</t>
+          <t>55813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109268</t>
+          <t>107663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64585</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>91222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>141514</t>
+          <t>150867</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112017</t>
+          <t>117524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181203</t>
+          <t>183838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>313503</t>
+          <t>349578</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>289467</t>
+          <t>317722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335240</t>
+          <t>373398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>421354</t>
+          <t>402511</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398607</t>
+          <t>383134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458588</t>
+          <t>421046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>734857</t>
+          <t>752089</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698368</t>
+          <t>717127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783861</t>
+          <t>780965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100432</t>
+          <t>117743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>93602</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125550</t>
+          <t>147569</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77969</t>
+          <t>85369</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>68662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99011</t>
+          <t>103288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>178401</t>
+          <t>203112</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>133884</t>
+          <t>174971</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>212124</t>
+          <t>237925</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,17 +13094,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>34486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>934889</t>
+          <t>976535</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934889</t>
+          <t>976535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934889</t>
+          <t>976535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>421381</t>
+          <t>489044</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>400210</t>
+          <t>465916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>440560</t>
+          <t>510015</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>457284</t>
+          <t>524759</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>442671</t>
+          <t>509353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>469870</t>
+          <t>541980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>878664</t>
+          <t>1013803</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>854277</t>
+          <t>985269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>900912</t>
+          <t>1040140</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>100342</t>
+          <t>115876</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81817</t>
+          <t>96058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119997</t>
+          <t>139976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74300</t>
+          <t>86171</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61809</t>
+          <t>71187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87925</t>
+          <t>102061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>174642</t>
+          <t>202047</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152339</t>
+          <t>177607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196834</t>
+          <t>230972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -13515,67 +13515,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11209</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6365</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10884</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>6230</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>17637</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>23279</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>33993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>532583</t>
+          <t>616990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>532583</t>
+          <t>616990</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>532583</t>
+          <t>616990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1075050</t>
+          <t>1239129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1075050</t>
+          <t>1239129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1075050</t>
+          <t>1239129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>788169</t>
+          <t>589361</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>738508</t>
+          <t>567116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>841994</t>
+          <t>608123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>616426</t>
+          <t>632525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>601575</t>
+          <t>617365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>635024</t>
+          <t>647666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1404594</t>
+          <t>1221886</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1360030</t>
+          <t>1198790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1487387</t>
+          <t>1248574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86305</t>
+          <t>94867</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39483</t>
+          <t>76278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129509</t>
+          <t>114736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82427</t>
+          <t>88577</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65976</t>
+          <t>74352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96968</t>
+          <t>103565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>168732</t>
+          <t>183444</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97501</t>
+          <t>159573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208756</t>
+          <t>206467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>40248</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886659</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886659</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886659</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>711148</t>
+          <t>734976</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>711148</t>
+          <t>734976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>711148</t>
+          <t>734976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1597807</t>
+          <t>1434405</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597807</t>
+          <t>1434405</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597807</t>
+          <t>1434405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>485786</t>
+          <t>527284</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>469931</t>
+          <t>511925</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>499910</t>
+          <t>543637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>483816</t>
+          <t>536450</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>472097</t>
+          <t>524529</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>495073</t>
+          <t>548476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1063735</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>948758</t>
+          <t>1041305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>986349</t>
+          <t>1082221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61766</t>
+          <t>68267</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49971</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76496</t>
+          <t>83593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>55444</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>51680</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>74263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>117210</t>
+          <t>131162</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101904</t>
+          <t>112199</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135435</t>
+          <t>151621</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,27 +14462,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560228</t>
+          <t>608296</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560228</t>
+          <t>608296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560228</t>
+          <t>608296</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547356</t>
+          <t>608219</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547356</t>
+          <t>608219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547356</t>
+          <t>608219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1107584</t>
+          <t>1216515</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1107584</t>
+          <t>1216515</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1107584</t>
+          <t>1216515</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>333681</t>
+          <t>365761</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>322826</t>
+          <t>354385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>341309</t>
+          <t>375012</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>579733</t>
+          <t>408268</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>561561</t>
+          <t>400337</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>598088</t>
+          <t>415395</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>913414</t>
+          <t>774027</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>892375</t>
+          <t>759258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>944476</t>
+          <t>786077</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41572</t>
+          <t>48413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24892</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41129</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>64370</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>52513</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75419</t>
+          <t>77916</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>406014</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>406014</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>406014</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>974883</t>
+          <t>844571</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>974883</t>
+          <t>844571</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>974883</t>
+          <t>844571</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>261308</t>
+          <t>286154</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>254380</t>
+          <t>277467</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267597</t>
+          <t>292431</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>405770</t>
+          <t>442820</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>398787</t>
+          <t>434747</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>410934</t>
+          <t>448774</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>667078</t>
+          <t>728974</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>656986</t>
+          <t>719097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>675351</t>
+          <t>738662</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26408</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19131</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>42953</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>53229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -15339,27 +15339,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>383</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>992</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -15384,12 +15384,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -15409,22 +15409,22 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>309855</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>309855</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>309855</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708249</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708249</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708249</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2920513</t>
+          <t>2927068</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2850514</t>
+          <t>2868717</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3036571</t>
+          <t>2978530</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3208677</t>
+          <t>3233269</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3160073</t>
+          <t>3191955</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3291561</t>
+          <t>3270933</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6129190</t>
+          <t>6160337</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6040436</t>
+          <t>6089655</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6261619</t>
+          <t>6221444</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>476728</t>
+          <t>537993</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368642</t>
+          <t>485319</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>540816</t>
+          <t>593230</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>398747</t>
+          <t>439962</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>319593</t>
+          <t>404162</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>442190</t>
+          <t>478418</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>875475</t>
+          <t>977955</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>919849</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>956689</t>
+          <t>1046423</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39776</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77503</t>
+          <t>80260</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>84783</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>141205</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
